--- a/artfynd/Stockbäcken artfynd.xlsx
+++ b/artfynd/Stockbäcken artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>375618</v>
+        <v>56071571</v>
       </c>
       <c r="B2" t="n">
-        <v>91259</v>
+        <v>78334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>708639</v>
+        <v>708397</v>
       </c>
       <c r="R2" t="n">
-        <v>7070283</v>
+        <v>7070143</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -756,31 +760,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>344332</v>
+        <v>56071572</v>
       </c>
       <c r="B3" t="n">
-        <v>91259</v>
+        <v>79917</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,34 +787,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1204</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>708762</v>
+        <v>708404</v>
       </c>
       <c r="R3" t="n">
-        <v>7070666</v>
+        <v>7070148</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -858,36 +861,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>344331</v>
+        <v>56826110</v>
       </c>
       <c r="B4" t="n">
-        <v>91259</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>708650</v>
+        <v>708400</v>
       </c>
       <c r="R4" t="n">
-        <v>7070604</v>
+        <v>7071143</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gränsticka vid basen och vedticka högre upp på samma låga</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,35 +959,35 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56071579</v>
+        <v>56826113</v>
       </c>
       <c r="B5" t="n">
-        <v>91245</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1012,17 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>708639</v>
+        <v>708373</v>
       </c>
       <c r="R5" t="n">
-        <v>7070398</v>
+        <v>7071045</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,12 +1049,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,61 +1065,71 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56826113</v>
+        <v>98688</v>
       </c>
       <c r="B6" t="n">
-        <v>91245</v>
+        <v>92123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>48</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>708373</v>
+        <v>708740</v>
       </c>
       <c r="R6" t="n">
-        <v>7071045</v>
+        <v>7070666</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1162,12 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1179,35 +1173,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>granlåga</t>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>396587</v>
+        <v>98689</v>
       </c>
       <c r="B7" t="n">
-        <v>91699</v>
+        <v>92123</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1215,21 +1204,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>708753</v>
+        <v>708719</v>
       </c>
       <c r="R7" t="n">
-        <v>7070589</v>
+        <v>7070626</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,45 +1295,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>98688</v>
+        <v>56826122</v>
       </c>
       <c r="B8" t="n">
-        <v>91446</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>708740</v>
+        <v>708455</v>
       </c>
       <c r="R8" t="n">
-        <v>7070666</v>
+        <v>7070561</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,12 +1360,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,30 +1377,35 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1569800</v>
+        <v>162863</v>
       </c>
       <c r="B9" t="n">
-        <v>91263</v>
+        <v>89292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,37 +1413,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>708668</v>
+        <v>708740</v>
       </c>
       <c r="R9" t="n">
-        <v>7070402</v>
+        <v>7070666</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1473,12 +1467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1493,27 +1487,32 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17225141</v>
+        <v>56071577</v>
       </c>
       <c r="B10" t="n">
-        <v>80083</v>
+        <v>89292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1521,34 +1520,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>708490</v>
+        <v>708572</v>
       </c>
       <c r="R10" t="n">
-        <v>7070679</v>
+        <v>7070338</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1575,12 +1578,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,48 +1594,26 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AN10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>1 substratenheter # asp # Populus tremula</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>56071580</v>
       </c>
       <c r="B11" t="n">
-        <v>88654</v>
+        <v>89292</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1730,10 +1711,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56826118</v>
+        <v>299350</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,21 +1722,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,13 +1746,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>708632</v>
+        <v>708559</v>
       </c>
       <c r="R12" t="n">
-        <v>7070854</v>
+        <v>7070252</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1795,12 +1776,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,35 +1793,35 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56826089</v>
+        <v>299351</v>
       </c>
       <c r="B13" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>708972</v>
+        <v>708693</v>
       </c>
       <c r="R13" t="n">
-        <v>7070903</v>
+        <v>7070523</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,12 +1883,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,35 +1900,35 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>torrgran/granlåga</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1546971</v>
+        <v>426323</v>
       </c>
       <c r="B14" t="n">
-        <v>91263</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,37 +1936,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>708656</v>
+        <v>708613</v>
       </c>
       <c r="R14" t="n">
-        <v>7070516</v>
+        <v>7070346</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2009,12 +1990,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,54 +2010,49 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17225132</v>
+        <v>426324</v>
       </c>
       <c r="B15" t="n">
-        <v>91699</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2062,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>708661</v>
+        <v>708670</v>
       </c>
       <c r="R15" t="n">
-        <v>7070461</v>
+        <v>7070564</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2133,47 +2109,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran # Picea abies</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56826090</v>
+        <v>56071578</v>
       </c>
       <c r="B16" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2181,34 +2140,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>708967</v>
+        <v>708643</v>
       </c>
       <c r="R16" t="n">
-        <v>7070914</v>
+        <v>7070362</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,12 +2198,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2251,36 +2214,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56826102</v>
+        <v>56071579</v>
       </c>
       <c r="B17" t="n">
-        <v>82792</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,34 +2241,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>708643</v>
+        <v>708639</v>
       </c>
       <c r="R17" t="n">
-        <v>7071063</v>
+        <v>7070398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2342,12 +2299,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2358,36 +2315,26 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>396586</v>
+        <v>344327</v>
       </c>
       <c r="B18" t="n">
-        <v>91699</v>
+        <v>91923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2395,37 +2342,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>708760</v>
+        <v>708815</v>
       </c>
       <c r="R18" t="n">
-        <v>7070651</v>
+        <v>7070673</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2449,17 +2396,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Även gränsticka</t>
+          <t>på en låga som ligger rakt över bäcken. Fruktkroppen sitter precis över bäcken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2474,65 +2421,70 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1569799</v>
+        <v>344328</v>
       </c>
       <c r="B19" t="n">
-        <v>91263</v>
+        <v>91923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>708632</v>
+        <v>708801</v>
       </c>
       <c r="R19" t="n">
-        <v>7070278</v>
+        <v>7070686</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2556,12 +2508,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,66 +2528,67 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>56071576</v>
+        <v>344329</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>91923</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>708533</v>
+        <v>708733</v>
       </c>
       <c r="R20" t="n">
-        <v>7070310</v>
+        <v>7070656</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2662,12 +2615,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,48 +2631,58 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>56826108</v>
+        <v>344330</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>91923</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,13 +2692,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>708435</v>
+        <v>708628</v>
       </c>
       <c r="R21" t="n">
-        <v>7071092</v>
+        <v>7070270</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2759,12 +2722,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2776,57 +2739,57 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56826109</v>
+        <v>344331</v>
       </c>
       <c r="B22" t="n">
-        <v>79012</v>
+        <v>91923</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,10 +2799,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>708414</v>
+        <v>708650</v>
       </c>
       <c r="R22" t="n">
-        <v>7071104</v>
+        <v>7070604</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2866,12 +2829,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gränsticka vid basen och vedticka högre upp på samma låga</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2883,57 +2851,57 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56826117</v>
+        <v>344332</v>
       </c>
       <c r="B23" t="n">
-        <v>79012</v>
+        <v>91923</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2943,10 +2911,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>708587</v>
+        <v>708762</v>
       </c>
       <c r="R23" t="n">
-        <v>7070979</v>
+        <v>7070666</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2973,12 +2941,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2990,73 +2958,73 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1546970</v>
+        <v>375618</v>
       </c>
       <c r="B24" t="n">
-        <v>91263</v>
+        <v>91923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>708671</v>
+        <v>708639</v>
       </c>
       <c r="R24" t="n">
-        <v>7070387</v>
+        <v>7070283</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3080,12 +3048,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3100,54 +3068,49 @@
       <c r="AH24" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>426324</v>
+        <v>375619</v>
       </c>
       <c r="B25" t="n">
-        <v>91245</v>
+        <v>91923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3157,10 +3120,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>708670</v>
+        <v>708639</v>
       </c>
       <c r="R25" t="n">
-        <v>7070564</v>
+        <v>7070578</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3224,14 +3187,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>17225135</v>
+        <v>375620</v>
       </c>
       <c r="B26" t="n">
-        <v>91259</v>
+        <v>91923</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3259,13 +3222,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>708639</v>
+        <v>708724</v>
       </c>
       <c r="R26" t="n">
-        <v>7070578</v>
+        <v>7070657</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3306,47 +3269,30 @@
       <c r="AG26" t="b">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran # Picea abies</t>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Via SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>56826093</v>
+        <v>382765</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3354,21 +3300,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,13 +3324,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708868</v>
+        <v>708771</v>
       </c>
       <c r="R27" t="n">
-        <v>7070919</v>
+        <v>7070689</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3408,12 +3354,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3425,35 +3371,35 @@
       <c r="AG27" t="b">
         <v>0</v>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56826126</v>
+        <v>382766</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3461,21 +3407,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3485,10 +3431,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708759</v>
+        <v>708771</v>
       </c>
       <c r="R28" t="n">
-        <v>7070735</v>
+        <v>7070606</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3515,12 +3461,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ullticka på samma låga</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3532,35 +3483,35 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>56826119</v>
+        <v>396585</v>
       </c>
       <c r="B29" t="n">
-        <v>78739</v>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3568,34 +3519,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708539</v>
+        <v>708661</v>
       </c>
       <c r="R29" t="n">
-        <v>7070736</v>
+        <v>7070461</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3622,12 +3573,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,35 +3590,30 @@
       <c r="AG29" t="b">
         <v>0</v>
       </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>56826099</v>
+        <v>396586</v>
       </c>
       <c r="B30" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3675,34 +3621,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708714</v>
+        <v>708760</v>
       </c>
       <c r="R30" t="n">
-        <v>7070984</v>
+        <v>7070651</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3729,12 +3675,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2012-10-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Även gränsticka</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,35 +3697,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>gran</t>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>56826094</v>
+        <v>396587</v>
       </c>
       <c r="B31" t="n">
-        <v>78980</v>
+        <v>92369</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3782,34 +3728,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708805</v>
+        <v>708753</v>
       </c>
       <c r="R31" t="n">
-        <v>7070899</v>
+        <v>7070589</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3836,12 +3782,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3853,35 +3799,30 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>gran</t>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>56071577</v>
+        <v>364209</v>
       </c>
       <c r="B32" t="n">
-        <v>88654</v>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,38 +3830,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>708572</v>
+        <v>708690</v>
       </c>
       <c r="R32" t="n">
-        <v>7070338</v>
+        <v>7070551</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3947,12 +3884,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3963,64 +3900,69 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>375620</v>
+        <v>1672404</v>
       </c>
       <c r="B33" t="n">
-        <v>91259</v>
+        <v>91872</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>708724</v>
+        <v>708775</v>
       </c>
       <c r="R33" t="n">
-        <v>7070657</v>
+        <v>7070734</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4044,12 +3986,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2007-10-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På många lågor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4064,49 +4011,54 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2053261</v>
+        <v>1830053</v>
       </c>
       <c r="B34" t="n">
-        <v>80112</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4116,13 +4068,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708676</v>
+        <v>708656</v>
       </c>
       <c r="R34" t="n">
-        <v>7070547</v>
+        <v>7070516</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4154,6 +4106,11 @@
           <t>2007-10-18</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4170,7 +4127,7 @@
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Sälg</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4188,14 +4145,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>56826127</v>
+        <v>56071576</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4216,17 +4173,21 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708917</v>
+        <v>708533</v>
       </c>
       <c r="R35" t="n">
-        <v>7070846</v>
+        <v>7070310</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4253,12 +4214,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4269,58 +4230,48 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>gran, rikligt</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>56826103</v>
+        <v>56826120</v>
       </c>
       <c r="B36" t="n">
-        <v>78739</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4330,10 +4281,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708539</v>
+        <v>708484</v>
       </c>
       <c r="R36" t="n">
-        <v>7071115</v>
+        <v>7070628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4384,7 +4335,7 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4402,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>17225142</v>
+        <v>56826121</v>
       </c>
       <c r="B37" t="n">
-        <v>91446</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4413,34 +4364,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708719</v>
+        <v>708464</v>
       </c>
       <c r="R37" t="n">
-        <v>7070626</v>
+        <v>7070612</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4467,12 +4418,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4484,51 +4435,39 @@
       <c r="AG37" t="b">
         <v>0</v>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>56826120</v>
+        <v>56826123</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4556,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708484</v>
+        <v>708509</v>
       </c>
       <c r="R38" t="n">
-        <v>7070628</v>
+        <v>7070534</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4628,32 +4567,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>56826087</v>
+        <v>56826124</v>
       </c>
       <c r="B39" t="n">
-        <v>95594</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4663,10 +4602,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708998</v>
+        <v>708563</v>
       </c>
       <c r="R39" t="n">
-        <v>7070851</v>
+        <v>7070614</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4713,6 +4652,11 @@
       <c r="AI39" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -4730,45 +4674,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>426323</v>
+        <v>56826126</v>
       </c>
       <c r="B40" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708613</v>
+        <v>708759</v>
       </c>
       <c r="R40" t="n">
-        <v>7070346</v>
+        <v>7070735</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4795,12 +4739,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4812,30 +4756,35 @@
       <c r="AG40" t="b">
         <v>0</v>
       </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>SCA Naturvärdesinventeringar</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Via SCA Naturvärdesinventeringar</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1546972</v>
+        <v>1999943</v>
       </c>
       <c r="B41" t="n">
-        <v>91263</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4843,37 +4792,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stockbäcken, Ång</t>
+          <t>Lillsjökullarna-Storåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708770</v>
+        <v>708490</v>
       </c>
       <c r="R41" t="n">
-        <v>7070823</v>
+        <v>7070679</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4897,12 +4846,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2012-10-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4917,54 +4866,49 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Gran</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Via SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>56826124</v>
+        <v>2053261</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>80461</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4974,10 +4918,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708563</v>
+        <v>708676</v>
       </c>
       <c r="R42" t="n">
-        <v>7070614</v>
+        <v>7070547</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5004,12 +4948,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5021,35 +4965,35 @@
       <c r="AG42" t="b">
         <v>0</v>
       </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>56071578</v>
+        <v>56071573</v>
       </c>
       <c r="B43" t="n">
-        <v>91245</v>
+        <v>79085</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5057,21 +5001,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5085,10 +5029,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708643</v>
+        <v>708441</v>
       </c>
       <c r="R43" t="n">
-        <v>7070362</v>
+        <v>7070237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5147,32 +5091,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>56826114</v>
+        <v>56826119</v>
       </c>
       <c r="B44" t="n">
-        <v>79956</v>
+        <v>79085</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>392</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Aspgelélav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Collema subnigrescens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Degel.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5182,10 +5126,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>708488</v>
+        <v>708539</v>
       </c>
       <c r="R44" t="n">
-        <v>7071024</v>
+        <v>7070736</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5236,7 +5180,7 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5254,10 +5198,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>56826116</v>
+        <v>56071574</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5265,34 +5209,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708556</v>
+        <v>708491</v>
       </c>
       <c r="R45" t="n">
-        <v>7070992</v>
+        <v>7070268</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5319,12 +5267,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2015-10-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5335,36 +5283,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>17225133</v>
+        <v>56826095</v>
       </c>
       <c r="B46" t="n">
-        <v>82792</v>
+        <v>79359</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5372,34 +5310,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lillsjökullarna-Storåsen, Ång</t>
+          <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708690</v>
+        <v>708805</v>
       </c>
       <c r="R46" t="n">
-        <v>7070551</v>
+        <v>7070899</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5426,12 +5364,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2012-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5443,47 +5381,35 @@
       <c r="AG46" t="b">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
         <is>
           <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gran # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>56826104</v>
+        <v>56826109</v>
       </c>
       <c r="B47" t="n">
-        <v>79569</v>
+        <v>79359</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5491,21 +5417,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5515,10 +5441,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708539</v>
+        <v>708414</v>
       </c>
       <c r="R47" t="n">
-        <v>7071115</v>
+        <v>7071104</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5569,7 +5495,7 @@
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -5587,10 +5513,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>56826122</v>
+        <v>56826117</v>
       </c>
       <c r="B48" t="n">
-        <v>79012</v>
+        <v>79359</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5622,10 +5548,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>708455</v>
+        <v>708587</v>
       </c>
       <c r="R48" t="n">
-        <v>7070561</v>
+        <v>7070979</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5694,32 +5620,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>299351</v>
+        <v>56826114</v>
       </c>
       <c r="B49" t="n">
-        <v>91245</v>
+        <v>80305</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5729,10 +5655,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708693</v>
+        <v>708488</v>
       </c>
       <c r="R49" t="n">
-        <v>7070523</v>
+        <v>7071024</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5759,12 +5685,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5776,57 +5702,57 @@
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>382765</v>
+        <v>56826092</v>
       </c>
       <c r="B50" t="n">
-        <v>91699</v>
+        <v>89292</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>510</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5836,13 +5762,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708771</v>
+        <v>708960</v>
       </c>
       <c r="R50" t="n">
-        <v>7070689</v>
+        <v>7070924</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5866,12 +5792,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5883,35 +5809,35 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>56071571</v>
+        <v>56826090</v>
       </c>
       <c r="B51" t="n">
-        <v>77929</v>
+        <v>83173</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5919,38 +5845,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>708397</v>
+        <v>708967</v>
       </c>
       <c r="R51" t="n">
-        <v>7070143</v>
+        <v>7070914</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5977,12 +5899,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5993,26 +5915,36 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>56071572</v>
+        <v>56826102</v>
       </c>
       <c r="B52" t="n">
-        <v>79569</v>
+        <v>83173</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6020,38 +5952,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>708404</v>
+        <v>708643</v>
       </c>
       <c r="R52" t="n">
-        <v>7070148</v>
+        <v>7071063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6078,12 +6006,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6094,75 +6022,74 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>56374410</v>
+        <v>56826128</v>
       </c>
       <c r="B53" t="n">
-        <v>57761</v>
+        <v>83173</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103031</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708770</v>
+        <v>708948</v>
       </c>
       <c r="R53" t="n">
-        <v>7070823</v>
+        <v>7070843</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6186,12 +6113,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6202,48 +6129,58 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>gammal gran</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>56826096</v>
+        <v>56826100</v>
       </c>
       <c r="B54" t="n">
-        <v>91263</v>
+        <v>91872</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6253,10 +6190,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708766</v>
+        <v>708708</v>
       </c>
       <c r="R54" t="n">
-        <v>7070876</v>
+        <v>7071002</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6307,7 +6244,7 @@
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>högstubbe gran</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -6325,32 +6262,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1672404</v>
+        <v>56826093</v>
       </c>
       <c r="B55" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6360,13 +6297,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>708775</v>
+        <v>708868</v>
       </c>
       <c r="R55" t="n">
-        <v>7070734</v>
+        <v>7070919</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6390,17 +6327,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>På många lågor</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6412,57 +6344,57 @@
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>299350</v>
+        <v>56826094</v>
       </c>
       <c r="B56" t="n">
-        <v>91245</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6472,13 +6404,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>708559</v>
+        <v>708805</v>
       </c>
       <c r="R56" t="n">
-        <v>7070252</v>
+        <v>7070899</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6502,12 +6434,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6519,57 +6451,57 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56826088</v>
+        <v>56826097</v>
       </c>
       <c r="B57" t="n">
-        <v>75080</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6579,10 +6511,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708970</v>
+        <v>708765</v>
       </c>
       <c r="R57" t="n">
-        <v>7070894</v>
+        <v>7070877</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6633,7 +6565,7 @@
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>björkstubbe</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -6651,32 +6583,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>56826100</v>
+        <v>56826098</v>
       </c>
       <c r="B58" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6686,10 +6618,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708708</v>
+        <v>708731</v>
       </c>
       <c r="R58" t="n">
-        <v>7071002</v>
+        <v>7070904</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6740,7 +6672,7 @@
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -6758,32 +6690,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>56826110</v>
+        <v>56826099</v>
       </c>
       <c r="B59" t="n">
-        <v>79012</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6793,10 +6725,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708400</v>
+        <v>708714</v>
       </c>
       <c r="R59" t="n">
-        <v>7071143</v>
+        <v>7070984</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6865,32 +6797,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>56826086</v>
+        <v>56826101</v>
       </c>
       <c r="B60" t="n">
-        <v>91210</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6900,10 +6832,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>708998</v>
+        <v>708673</v>
       </c>
       <c r="R60" t="n">
-        <v>7070856</v>
+        <v>7071044</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6954,7 +6886,7 @@
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>granlåga</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -6972,10 +6904,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>382766</v>
+        <v>56826108</v>
       </c>
       <c r="B61" t="n">
-        <v>91699</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6983,21 +6915,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7007,10 +6939,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708771</v>
+        <v>708435</v>
       </c>
       <c r="R61" t="n">
-        <v>7070606</v>
+        <v>7071092</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7037,17 +6969,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ullticka på samma låga</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7059,74 +6986,70 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>56071574</v>
+        <v>56826116</v>
       </c>
       <c r="B62" t="n">
-        <v>79569</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708491</v>
+        <v>708556</v>
       </c>
       <c r="R62" t="n">
-        <v>7070268</v>
+        <v>7070992</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7153,12 +7076,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7169,30 +7092,40 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1830053</v>
+        <v>56826118</v>
       </c>
       <c r="B63" t="n">
-        <v>78980</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -7220,13 +7153,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>708656</v>
+        <v>708632</v>
       </c>
       <c r="R63" t="n">
-        <v>7070516</v>
+        <v>7070854</v>
       </c>
       <c r="S63" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7250,17 +7183,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7272,57 +7200,57 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>162863</v>
+        <v>56826127</v>
       </c>
       <c r="B64" t="n">
-        <v>88654</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7332,13 +7260,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>708740</v>
+        <v>708917</v>
       </c>
       <c r="R64" t="n">
-        <v>7070666</v>
+        <v>7070846</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7362,12 +7290,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7379,35 +7307,35 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>gran, rikligt</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>344329</v>
+        <v>56826105</v>
       </c>
       <c r="B65" t="n">
-        <v>91259</v>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7415,21 +7343,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7439,10 +7367,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708733</v>
+        <v>708487</v>
       </c>
       <c r="R65" t="n">
-        <v>7070656</v>
+        <v>7071123</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7469,12 +7397,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7486,35 +7414,35 @@
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>silverstubbe tall</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>344328</v>
+        <v>56374410</v>
       </c>
       <c r="B66" t="n">
-        <v>91259</v>
+        <v>58057</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7522,37 +7450,48 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1204</v>
+        <v>103031</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708801</v>
+        <v>708770</v>
       </c>
       <c r="R66" t="n">
-        <v>7070686</v>
+        <v>7070823</v>
       </c>
       <c r="S66" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7592,16 +7531,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -7618,10 +7547,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>344327</v>
+        <v>56826103</v>
       </c>
       <c r="B67" t="n">
-        <v>91259</v>
+        <v>79085</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7629,21 +7558,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7653,13 +7582,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708815</v>
+        <v>708539</v>
       </c>
       <c r="R67" t="n">
-        <v>7070673</v>
+        <v>7071115</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7683,17 +7612,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>på en låga som ligger rakt över bäcken. Fruktkroppen sitter precis över bäcken</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7705,35 +7629,35 @@
       <c r="AG67" t="b">
         <v>0</v>
       </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>299349</v>
+        <v>56826104</v>
       </c>
       <c r="B68" t="n">
-        <v>91245</v>
+        <v>79917</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7741,21 +7665,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7765,13 +7689,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>709018</v>
+        <v>708539</v>
       </c>
       <c r="R68" t="n">
-        <v>7070851</v>
+        <v>7071115</v>
       </c>
       <c r="S68" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7795,17 +7719,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>på två lågor</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7817,35 +7736,35 @@
       <c r="AG68" t="b">
         <v>0</v>
       </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>56071573</v>
+        <v>56826107</v>
       </c>
       <c r="B69" t="n">
-        <v>78739</v>
+        <v>79917</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7853,38 +7772,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stockbäcken, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708441</v>
+        <v>708487</v>
       </c>
       <c r="R69" t="n">
-        <v>7070237</v>
+        <v>7071123</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7911,12 +7826,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2015-10-19</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7927,26 +7842,36 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>silverstubbe tall</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Julia Pettersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>56826123</v>
+        <v>299349</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>91909</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7954,21 +7879,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7978,13 +7903,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>708509</v>
+        <v>709018</v>
       </c>
       <c r="R70" t="n">
-        <v>7070534</v>
+        <v>7070851</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8008,12 +7933,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2007-10-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2007-10-18</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>på två lågor</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8025,35 +7955,35 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>56826098</v>
+        <v>56826088</v>
       </c>
       <c r="B71" t="n">
-        <v>78980</v>
+        <v>83312</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8061,21 +7991,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8085,10 +8015,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>708731</v>
+        <v>708970</v>
       </c>
       <c r="R71" t="n">
-        <v>7070904</v>
+        <v>7070894</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8139,7 +8069,7 @@
       </c>
       <c r="AO71" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkstubbe</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8157,32 +8087,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>56826095</v>
+        <v>56826087</v>
       </c>
       <c r="B72" t="n">
-        <v>79012</v>
+        <v>96338</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>185</v>
+        <v>2809</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8192,10 +8122,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708805</v>
+        <v>708998</v>
       </c>
       <c r="R72" t="n">
-        <v>7070899</v>
+        <v>7070851</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8242,11 +8172,6 @@
       <c r="AI72" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>gran</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8264,32 +8189,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>56826107</v>
+        <v>56826086</v>
       </c>
       <c r="B73" t="n">
-        <v>79569</v>
+        <v>91872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>5447</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8299,10 +8224,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708487</v>
+        <v>708998</v>
       </c>
       <c r="R73" t="n">
-        <v>7071123</v>
+        <v>7070856</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8353,7 +8278,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>silverstubbe tall</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8368,755 +8293,6 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>56826105</v>
-      </c>
-      <c r="B74" t="n">
-        <v>79598</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Hertelidea botryosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>708487</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7071123</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>silverstubbe tall</t>
-        </is>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>56826092</v>
-      </c>
-      <c r="B75" t="n">
-        <v>88654</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>510</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Cystostereum murrayi</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>708960</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7070924</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>torrgran</t>
-        </is>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>56826121</v>
-      </c>
-      <c r="B76" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>708464</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7070612</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>56826101</v>
-      </c>
-      <c r="B77" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>708673</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7071044</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>56826128</v>
-      </c>
-      <c r="B78" t="n">
-        <v>82792</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>708948</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7070843</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>gammal gran</t>
-        </is>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>56826097</v>
-      </c>
-      <c r="B79" t="n">
-        <v>78980</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E79" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q79" t="n">
-        <v>708765</v>
-      </c>
-      <c r="R79" t="n">
-        <v>7070877</v>
-      </c>
-      <c r="S79" t="n">
-        <v>10</v>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>2015-05-18</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>2015-10-30</t>
-        </is>
-      </c>
-      <c r="AD79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AT79" t="inlineStr"/>
-      <c r="AW79" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>Sebastian Kirppu</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>344330</v>
-      </c>
-      <c r="B80" t="n">
-        <v>91259</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E80" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Phellopilus nigrolimitatus</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Stockbäcken, Ång</t>
-        </is>
-      </c>
-      <c r="Q80" t="n">
-        <v>708628</v>
-      </c>
-      <c r="R80" t="n">
-        <v>7070270</v>
-      </c>
-      <c r="S80" t="n">
-        <v>25</v>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V80" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y80" t="inlineStr">
-        <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>2007-10-18</t>
-        </is>
-      </c>
-      <c r="AD80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
-      </c>
-      <c r="AT80" t="inlineStr"/>
-      <c r="AW80" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
